--- a/SampleLookupTable.xlsx
+++ b/SampleLookupTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://esrica-my.sharepoint.com/personal/fhoque_esri_ca/Documents/Documents/Living Atlas/Farah_LA_2025/LivingAtlasDashboard/LA_ItemsMetadata_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_C94BC0B7935BEC0F6235547658A966FAC9DABA70" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D360AD17-3160-4790-BC49-B5CC3AF1797D}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_C94BC0B7935BEC0F6235547658A966FAC9DABA70" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCFA685A-71C9-4765-B9A7-D0CAA8495963}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="180" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="perimeters_0" sheetId="1" r:id="rId1"/>
@@ -20,22 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
-  <si>
-    <t>field</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>OBJECTID</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>UID</t>
   </si>
@@ -88,9 +73,6 @@
     <t>countOrAmount</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>The province and/or territory the perimeter covers.</t>
   </si>
   <si>
@@ -101,6 +83,21 @@
   </si>
   <si>
     <t>The date and time the hotspot was last detected in the perimeter.</t>
+  </si>
+  <si>
+    <t>Unique Identifier</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ValueType</t>
   </si>
 </sst>
 </file>
@@ -156,10 +153,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -176,6 +176,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -463,121 +467,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.26953125" customWidth="1"/>
-    <col min="2" max="2" width="42.81640625" customWidth="1"/>
-    <col min="3" max="3" width="55.08984375" customWidth="1"/>
+    <col min="1" max="1" width="15" style="2" customWidth="1"/>
+    <col min="2" max="2" width="34.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.08984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.1796875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
